--- a/out/08_ISMS/SNX-ISMS-REG-01 Information Asset Register (Rev00 DRAFT).xlsx
+++ b/out/08_ISMS/SNX-ISMS-REG-01 Information Asset Register (Rev00 DRAFT).xlsx
@@ -14,8 +14,11 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pemusnahan" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
+    <definedName name="_xlnm.Print_Titles" localSheetId="2">'Daftar'!$1:$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Register Aset'!$A$4:$V$216</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="3">'Register Aset'!$4:$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Pemusnahan'!$A$4:$I$44</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="4">'Pemusnahan'!$4:$4</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.0001"/>
 </workbook>
@@ -169,7 +172,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="53">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -299,6 +302,33 @@
     </xf>
     <xf numFmtId="164" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -708,8 +738,15 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="15" customHeight="1" s="24">
-      <c r="A4" s="27" t="inlineStr">
+    <row r="3" s="24">
+      <c r="A3" s="44" t="n"/>
+      <c r="B3" s="44" t="n"/>
+      <c r="C3" s="44" t="n"/>
+      <c r="D3" s="44" t="n"/>
+      <c r="E3" s="44" t="n"/>
+    </row>
+    <row r="4" ht="16.5" customHeight="1" s="24">
+      <c r="A4" s="45" t="inlineStr">
         <is>
           <t>Nomor dokumen</t>
         </is>
@@ -719,9 +756,12 @@
           <t>SNX-ISMS-REG-01</t>
         </is>
       </c>
-    </row>
-    <row r="5" ht="15" customHeight="1" s="24">
-      <c r="A5" s="27" t="inlineStr">
+      <c r="C4" s="44" t="n"/>
+      <c r="D4" s="44" t="n"/>
+      <c r="E4" s="44" t="n"/>
+    </row>
+    <row r="5" ht="16.5" customHeight="1" s="24">
+      <c r="A5" s="45" t="inlineStr">
         <is>
           <t>Judul</t>
         </is>
@@ -731,9 +771,12 @@
           <t>Information Asset Register</t>
         </is>
       </c>
-    </row>
-    <row r="6" ht="15" customHeight="1" s="24">
-      <c r="A6" s="27" t="inlineStr">
+      <c r="C5" s="44" t="n"/>
+      <c r="D5" s="44" t="n"/>
+      <c r="E5" s="44" t="n"/>
+    </row>
+    <row r="6" ht="16.5" customHeight="1" s="24">
+      <c r="A6" s="45" t="inlineStr">
         <is>
           <t>Revisi</t>
         </is>
@@ -743,9 +786,12 @@
           <t>00 (DRAFT)</t>
         </is>
       </c>
-    </row>
-    <row r="7" ht="15" customHeight="1" s="24">
-      <c r="A7" s="27" t="inlineStr">
+      <c r="C6" s="44" t="n"/>
+      <c r="D6" s="44" t="n"/>
+      <c r="E6" s="44" t="n"/>
+    </row>
+    <row r="7" ht="16.5" customHeight="1" s="24">
+      <c r="A7" s="45" t="inlineStr">
         <is>
           <t>Tanggal draft</t>
         </is>
@@ -755,9 +801,12 @@
           <t>13 Oktober 2026</t>
         </is>
       </c>
-    </row>
-    <row r="8" ht="15" customHeight="1" s="24">
-      <c r="A8" s="27" t="inlineStr">
+      <c r="C7" s="44" t="n"/>
+      <c r="D7" s="44" t="n"/>
+      <c r="E7" s="44" t="n"/>
+    </row>
+    <row r="8" ht="16.5" customHeight="1" s="24">
+      <c r="A8" s="45" t="inlineStr">
         <is>
           <t>Tanggal efektif</t>
         </is>
@@ -767,9 +816,12 @@
           <t>Ditetapkan saat pengesahan</t>
         </is>
       </c>
-    </row>
-    <row r="9" ht="15" customHeight="1" s="24">
-      <c r="A9" s="27" t="inlineStr">
+      <c r="C8" s="44" t="n"/>
+      <c r="D8" s="44" t="n"/>
+      <c r="E8" s="44" t="n"/>
+    </row>
+    <row r="9" ht="16.5" customHeight="1" s="24">
+      <c r="A9" s="45" t="inlineStr">
         <is>
           <t>Klasifikasi</t>
         </is>
@@ -779,9 +831,12 @@
           <t>RESTRICTED (Internal)</t>
         </is>
       </c>
-    </row>
-    <row r="10" ht="15" customHeight="1" s="24">
-      <c r="A10" s="27" t="inlineStr">
+      <c r="C9" s="44" t="n"/>
+      <c r="D9" s="44" t="n"/>
+      <c r="E9" s="44" t="n"/>
+    </row>
+    <row r="10" ht="16.5" customHeight="1" s="24">
+      <c r="A10" s="45" t="inlineStr">
         <is>
           <t>Pemilik dokumen</t>
         </is>
@@ -791,9 +846,12 @@
           <t>Head of Operation</t>
         </is>
       </c>
-    </row>
-    <row r="11" ht="15" customHeight="1" s="24">
-      <c r="A11" s="27" t="inlineStr">
+      <c r="C10" s="44" t="n"/>
+      <c r="D10" s="44" t="n"/>
+      <c r="E10" s="44" t="n"/>
+    </row>
+    <row r="11" ht="16.5" customHeight="1" s="24">
+      <c r="A11" s="45" t="inlineStr">
         <is>
           <t>Disetujui oleh</t>
         </is>
@@ -803,9 +861,12 @@
           <t>Samuel Kristanto Utomo / President Director</t>
         </is>
       </c>
-    </row>
-    <row r="12" ht="15" customHeight="1" s="24">
-      <c r="A12" s="27" t="inlineStr">
+      <c r="C11" s="44" t="n"/>
+      <c r="D11" s="44" t="n"/>
+      <c r="E11" s="44" t="n"/>
+    </row>
+    <row r="12" ht="30" customHeight="1" s="24">
+      <c r="A12" s="45" t="inlineStr">
         <is>
           <t>Acuan ISO 9001:2015</t>
         </is>
@@ -815,9 +876,12 @@
           <t>Klausul 7.1.3</t>
         </is>
       </c>
-    </row>
-    <row r="13" ht="15" customHeight="1" s="24">
-      <c r="A13" s="27" t="inlineStr">
+      <c r="C12" s="44" t="n"/>
+      <c r="D12" s="44" t="n"/>
+      <c r="E12" s="44" t="n"/>
+    </row>
+    <row r="13" ht="30" customHeight="1" s="24">
+      <c r="A13" s="45" t="inlineStr">
         <is>
           <t>Acuan ISO/IEC 27001:2022</t>
         </is>
@@ -827,9 +891,12 @@
           <t>Kontrol Annex A 5.9, 5.10, 5.11, 5.12</t>
         </is>
       </c>
-    </row>
-    <row r="14" ht="15" customHeight="1" s="24">
-      <c r="A14" s="27" t="inlineStr">
+      <c r="C13" s="44" t="n"/>
+      <c r="D13" s="44" t="n"/>
+      <c r="E13" s="44" t="n"/>
+    </row>
+    <row r="14" ht="30" customHeight="1" s="24">
+      <c r="A14" s="45" t="inlineStr">
         <is>
           <t>Masa simpan record</t>
         </is>
@@ -839,153 +906,218 @@
           <t>Register Aset: berlaku sampai digantikan. Berita acara di sheet Pemusnahan: 5 tahun (SNX-ISMS-SOP-04).</t>
         </is>
       </c>
-    </row>
-    <row r="15" ht="23.85" customHeight="1" s="24">
-      <c r="A15" s="27" t="inlineStr">
+      <c r="C14" s="44" t="n"/>
+      <c r="D14" s="44" t="n"/>
+      <c r="E14" s="44" t="n"/>
+    </row>
+    <row r="15" ht="43.5" customHeight="1" s="24">
+      <c r="A15" s="45" t="inlineStr">
         <is>
           <t>Tujuan</t>
         </is>
       </c>
       <c r="B15" s="28" t="inlineStr">
         <is>
-          <t>Inventaris aset informasi dan aset TI beserta pemilik, klasifikasi, nilai CIA, status konfigurasi, dan siklus hidup.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="15" customHeight="1" s="24">
-      <c r="A17" s="29" t="inlineStr">
+          <t>Mencatat aset informasi dan aset TI beserta pemilik, klasifikasi, nilai CIA, status konfigurasi, dan siklus hidupnya.</t>
+        </is>
+      </c>
+      <c r="C15" s="44" t="n"/>
+      <c r="D15" s="44" t="n"/>
+      <c r="E15" s="44" t="n"/>
+    </row>
+    <row r="16" s="24">
+      <c r="A16" s="44" t="n"/>
+      <c r="B16" s="44" t="n"/>
+      <c r="C16" s="44" t="n"/>
+      <c r="D16" s="44" t="n"/>
+      <c r="E16" s="44" t="n"/>
+    </row>
+    <row r="17" ht="16.5" customHeight="1" s="24">
+      <c r="A17" s="46" t="inlineStr">
         <is>
           <t>Cara pakai</t>
         </is>
       </c>
-    </row>
-    <row r="18" ht="23.85" customHeight="1" s="24">
-      <c r="A18" s="30" t="inlineStr">
+      <c r="B17" s="44" t="n"/>
+      <c r="C17" s="44" t="n"/>
+      <c r="D17" s="44" t="n"/>
+      <c r="E17" s="44" t="n"/>
+    </row>
+    <row r="18" ht="30" customHeight="1" s="24">
+      <c r="A18" s="31" t="inlineStr">
         <is>
           <t>1.</t>
         </is>
       </c>
       <c r="B18" s="31" t="inlineStr">
         <is>
-          <t>Daftarkan setiap aset baru paling lambat saat mulai dipakai; aset pelanggan wajib sebelum gate G3.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="23.85" customHeight="1" s="24">
-      <c r="A19" s="30" t="inlineStr">
+          <t>Daftarkan setiap aset baru paling lambat saat aset mulai dipakai. Aset pelanggan wajib terdaftar sebelum gate G3.</t>
+        </is>
+      </c>
+      <c r="C18" s="44" t="n"/>
+      <c r="D18" s="44" t="n"/>
+      <c r="E18" s="44" t="n"/>
+    </row>
+    <row r="19" ht="30" customHeight="1" s="24">
+      <c r="A19" s="31" t="inlineStr">
         <is>
           <t>2.</t>
         </is>
       </c>
       <c r="B19" s="31" t="inlineStr">
         <is>
-          <t>Isi nilai C, I, A dengan skala 1 (rendah) sampai 3 (tinggi); nilai dan kritikalitas aset dihitung otomatis.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="15" customHeight="1" s="24">
-      <c r="A20" s="30" t="inlineStr">
+          <t>Isi nilai C, I, dan A dengan skala 1 (rendah) sampai 3 (tinggi). Nilai aset dan kritikalitas terisi otomatis.</t>
+        </is>
+      </c>
+      <c r="C19" s="44" t="n"/>
+      <c r="D19" s="44" t="n"/>
+      <c r="E19" s="44" t="n"/>
+    </row>
+    <row r="20" ht="30" customHeight="1" s="24">
+      <c r="A20" s="31" t="inlineStr">
         <is>
           <t>3.</t>
         </is>
       </c>
       <c r="B20" s="31" t="inlineStr">
         <is>
-          <t>Tandai CI = Ya untuk aset yang konfigurasinya dikendalikan dan isi acuan baseline.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="23.85" customHeight="1" s="24">
-      <c r="A21" s="30" t="inlineStr">
+          <t>Isi kolom CI dengan Ya untuk aset yang konfigurasinya dikendalikan, lalu isi Acuan baseline.</t>
+        </is>
+      </c>
+      <c r="C20" s="44" t="n"/>
+      <c r="D20" s="44" t="n"/>
+      <c r="E20" s="44" t="n"/>
+    </row>
+    <row r="21" ht="30" customHeight="1" s="24">
+      <c r="A21" s="31" t="inlineStr">
         <is>
           <t>4.</t>
         </is>
       </c>
       <c r="B21" s="31" t="inlineStr">
         <is>
-          <t>Review berikutnya dihitung otomatis 6 bulan setelah review terakhir; baris merah berarti review terlambat.</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="23.85" customHeight="1" s="24">
-      <c r="A22" s="30" t="inlineStr">
+          <t>Kolom Review berikutnya terisi otomatis, 6 bulan setelah Review terakhir. Baris merah menandakan review terlambat.</t>
+        </is>
+      </c>
+      <c r="C21" s="44" t="n"/>
+      <c r="D21" s="44" t="n"/>
+      <c r="E21" s="44" t="n"/>
+    </row>
+    <row r="22" ht="43.5" customHeight="1" s="24">
+      <c r="A22" s="31" t="inlineStr">
         <is>
           <t>5.</t>
         </is>
       </c>
       <c r="B22" s="31" t="inlineStr">
         <is>
-          <t>IP address dan detail teknis sensitif boleh dicatat di sini karena register berklasifikasi RESTRICTED; kredensial dilarang.</t>
-        </is>
-      </c>
+          <t>IP address dan detail teknis sensitif boleh dicatat di register ini karena klasifikasinya RESTRICTED. Kredensial tidak boleh dicatat.</t>
+        </is>
+      </c>
+      <c r="C22" s="44" t="n"/>
+      <c r="D22" s="44" t="n"/>
+      <c r="E22" s="44" t="n"/>
     </row>
     <row r="23" ht="23.85" customHeight="1" s="24">
-      <c r="A23" s="30" t="n"/>
+      <c r="A23" s="31" t="n"/>
       <c r="B23" s="31" t="n"/>
-    </row>
-    <row r="24"/>
-    <row r="25" ht="15" customHeight="1" s="24">
-      <c r="A25" s="29" t="inlineStr">
+      <c r="C23" s="44" t="n"/>
+      <c r="D23" s="44" t="n"/>
+      <c r="E23" s="44" t="n"/>
+    </row>
+    <row r="24" s="24">
+      <c r="A24" s="44" t="n"/>
+      <c r="B24" s="44" t="n"/>
+      <c r="C24" s="44" t="n"/>
+      <c r="D24" s="44" t="n"/>
+      <c r="E24" s="44" t="n"/>
+    </row>
+    <row r="25" ht="16.5" customHeight="1" s="24">
+      <c r="A25" s="46" t="inlineStr">
         <is>
           <t>Legenda warna</t>
         </is>
       </c>
-    </row>
-    <row r="26" ht="15" customHeight="1" s="24">
-      <c r="A26" s="32" t="n"/>
-      <c r="B26" s="30" t="inlineStr">
+      <c r="B25" s="44" t="n"/>
+      <c r="C25" s="44" t="n"/>
+      <c r="D25" s="44" t="n"/>
+      <c r="E25" s="44" t="n"/>
+    </row>
+    <row r="26" ht="16.5" customHeight="1" s="24">
+      <c r="A26" s="47" t="n"/>
+      <c r="B26" s="31" t="inlineStr">
         <is>
           <t>Sel input: diisi pengguna</t>
         </is>
       </c>
+      <c r="C26" s="44" t="n"/>
+      <c r="D26" s="44" t="n"/>
+      <c r="E26" s="44" t="n"/>
     </row>
     <row r="27" ht="15" customHeight="1" s="24">
-      <c r="A27" s="33" t="n"/>
-      <c r="B27" s="30" t="n"/>
-    </row>
-    <row r="28" ht="15" customHeight="1" s="24">
-      <c r="A28" s="34" t="n"/>
-      <c r="B28" s="30" t="inlineStr">
+      <c r="A27" s="48" t="n"/>
+      <c r="B27" s="31" t="n"/>
+      <c r="C27" s="44" t="n"/>
+      <c r="D27" s="44" t="n"/>
+      <c r="E27" s="44" t="n"/>
+    </row>
+    <row r="28" ht="16.5" customHeight="1" s="24">
+      <c r="A28" s="49" t="n"/>
+      <c r="B28" s="31" t="inlineStr">
         <is>
           <t>Sel rumus: jangan diubah</t>
         </is>
       </c>
-    </row>
-    <row r="30" ht="15" customHeight="1" s="24">
-      <c r="A30" s="29" t="inlineStr">
+      <c r="C28" s="44" t="n"/>
+      <c r="D28" s="44" t="n"/>
+      <c r="E28" s="44" t="n"/>
+    </row>
+    <row r="29" s="24">
+      <c r="A29" s="44" t="n"/>
+      <c r="B29" s="44" t="n"/>
+      <c r="C29" s="44" t="n"/>
+      <c r="D29" s="44" t="n"/>
+      <c r="E29" s="44" t="n"/>
+    </row>
+    <row r="30" ht="16.5" customHeight="1" s="24">
+      <c r="A30" s="46" t="inlineStr">
         <is>
           <t>Riwayat revisi</t>
         </is>
       </c>
-    </row>
-    <row r="31" ht="15" customHeight="1" s="24">
-      <c r="A31" s="35" t="inlineStr">
+      <c r="B30" s="44" t="n"/>
+      <c r="C30" s="44" t="n"/>
+      <c r="D30" s="44" t="n"/>
+      <c r="E30" s="44" t="n"/>
+    </row>
+    <row r="31" ht="16.5" customHeight="1" s="24">
+      <c r="A31" s="39" t="inlineStr">
         <is>
           <t>Revisi</t>
         </is>
       </c>
-      <c r="B31" s="35" t="inlineStr">
+      <c r="B31" s="39" t="inlineStr">
         <is>
           <t>Tanggal</t>
         </is>
       </c>
-      <c r="C31" s="35" t="inlineStr">
+      <c r="C31" s="39" t="inlineStr">
         <is>
           <t>Uraian perubahan</t>
         </is>
       </c>
-      <c r="D31" s="35" t="inlineStr">
+      <c r="D31" s="39" t="inlineStr">
         <is>
           <t>Disusun</t>
         </is>
       </c>
-      <c r="E31" s="35" t="inlineStr">
+      <c r="E31" s="39" t="inlineStr">
         <is>
           <t>Disetujui</t>
         </is>
       </c>
     </row>
-    <row r="32" ht="23.85" customHeight="1" s="24">
+    <row r="32" ht="30" customHeight="1" s="24">
       <c r="A32" s="28" t="inlineStr">
         <is>
           <t>00</t>
@@ -1019,77 +1151,91 @@
       <c r="D33" s="28" t="n"/>
       <c r="E33" s="28" t="n"/>
     </row>
-    <row r="34"/>
-    <row r="35" ht="15" customHeight="1" s="24">
-      <c r="A35" s="29" t="inlineStr">
+    <row r="34" s="24">
+      <c r="A34" s="44" t="n"/>
+      <c r="B34" s="44" t="n"/>
+      <c r="C34" s="44" t="n"/>
+      <c r="D34" s="44" t="n"/>
+      <c r="E34" s="44" t="n"/>
+    </row>
+    <row r="35" ht="16.5" customHeight="1" s="24">
+      <c r="A35" s="46" t="inlineStr">
         <is>
           <t>Pengesahan</t>
         </is>
       </c>
-    </row>
-    <row r="36" ht="15" customHeight="1" s="24">
-      <c r="A36" s="35" t="inlineStr">
+      <c r="B35" s="44" t="n"/>
+      <c r="C35" s="44" t="n"/>
+      <c r="D35" s="44" t="n"/>
+      <c r="E35" s="44" t="n"/>
+    </row>
+    <row r="36" ht="16.5" customHeight="1" s="24">
+      <c r="A36" s="39" t="inlineStr">
         <is>
           <t>Peran</t>
         </is>
       </c>
-      <c r="B36" s="35" t="inlineStr">
+      <c r="B36" s="39" t="inlineStr">
         <is>
           <t>Nama dan jabatan</t>
         </is>
       </c>
-      <c r="C36" s="35" t="inlineStr">
+      <c r="C36" s="39" t="inlineStr">
         <is>
           <t>Tanda tangan</t>
         </is>
       </c>
-      <c r="D36" s="35" t="inlineStr">
+      <c r="D36" s="39" t="inlineStr">
         <is>
           <t>Tanggal</t>
         </is>
       </c>
+      <c r="E36" s="44" t="n"/>
     </row>
     <row r="37" ht="27.75" customHeight="1" s="24">
-      <c r="A37" s="36" t="inlineStr">
+      <c r="A37" s="28" t="inlineStr">
         <is>
           <t>Disusun oleh</t>
         </is>
       </c>
-      <c r="B37" s="36" t="inlineStr">
+      <c r="B37" s="28" t="inlineStr">
         <is>
           <t>Erik Dwi Yanto / Technical/Operation Engineer L1</t>
         </is>
       </c>
-      <c r="C37" s="36" t="n"/>
-      <c r="D37" s="36" t="n"/>
+      <c r="C37" s="28" t="n"/>
+      <c r="D37" s="28" t="n"/>
+      <c r="E37" s="44" t="n"/>
     </row>
     <row r="38" ht="27.75" customHeight="1" s="24">
-      <c r="A38" s="36" t="inlineStr">
+      <c r="A38" s="28" t="inlineStr">
         <is>
           <t>Diperiksa oleh</t>
         </is>
       </c>
-      <c r="B38" s="36" t="inlineStr">
+      <c r="B38" s="28" t="inlineStr">
         <is>
           <t>Fani Fatullah / VP Tech Operation and Services</t>
         </is>
       </c>
-      <c r="C38" s="36" t="n"/>
-      <c r="D38" s="36" t="n"/>
+      <c r="C38" s="28" t="n"/>
+      <c r="D38" s="28" t="n"/>
+      <c r="E38" s="44" t="n"/>
     </row>
     <row r="39" ht="27.75" customHeight="1" s="24">
-      <c r="A39" s="36" t="inlineStr">
+      <c r="A39" s="28" t="inlineStr">
         <is>
           <t>Disetujui oleh</t>
         </is>
       </c>
-      <c r="B39" s="36" t="inlineStr">
+      <c r="B39" s="28" t="inlineStr">
         <is>
           <t>Samuel Kristanto Utomo / President Director</t>
         </is>
       </c>
-      <c r="C39" s="36" t="n"/>
-      <c r="D39" s="36" t="n"/>
+      <c r="C39" s="28" t="n"/>
+      <c r="D39" s="28" t="n"/>
+      <c r="E39" s="44" t="n"/>
     </row>
   </sheetData>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
@@ -1133,169 +1279,194 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="0"/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E10"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="25" customWidth="1" style="23" min="1" max="1"/>
-    <col width="16" customWidth="1" style="23" min="2" max="4"/>
+    <col width="17" customWidth="1" style="23" min="2" max="4"/>
+    <col width="13" customWidth="1" style="24" min="3" max="3"/>
+    <col width="13" customWidth="1" style="24" min="4" max="4"/>
     <col width="17" customWidth="1" style="23" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15" customHeight="1" s="24">
-      <c r="A1" s="38" t="inlineStr">
+    <row r="1" ht="16.5" customHeight="1" s="24">
+      <c r="A1" s="50" t="inlineStr">
         <is>
           <t>Jenis</t>
         </is>
       </c>
-      <c r="B1" s="38" t="inlineStr">
+      <c r="B1" s="50" t="inlineStr">
         <is>
           <t>Klasifikasi</t>
         </is>
       </c>
-      <c r="C1" s="38" t="inlineStr">
+      <c r="C1" s="50" t="inlineStr">
         <is>
           <t>CIA</t>
         </is>
       </c>
-      <c r="D1" s="38" t="inlineStr">
+      <c r="D1" s="50" t="inlineStr">
         <is>
           <t>YaTidak</t>
         </is>
       </c>
-      <c r="E1" s="38" t="inlineStr">
+      <c r="E1" s="50" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="15" customHeight="1" s="24">
-      <c r="A2" s="30" t="inlineStr">
+    <row r="2" ht="16.5" customHeight="1" s="24">
+      <c r="A2" s="51" t="inlineStr">
         <is>
           <t>Hardware</t>
         </is>
       </c>
-      <c r="B2" s="30" t="inlineStr">
+      <c r="B2" s="51" t="inlineStr">
         <is>
           <t>PUBLIC</t>
         </is>
       </c>
-      <c r="C2" s="30" t="n">
+      <c r="C2" s="51" t="n">
         <v>1</v>
       </c>
-      <c r="D2" s="30" t="inlineStr">
+      <c r="D2" s="51" t="inlineStr">
         <is>
           <t>Ya</t>
         </is>
       </c>
-      <c r="E2" s="30" t="inlineStr">
+      <c r="E2" s="51" t="inlineStr">
         <is>
           <t>Aktif</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="15" customHeight="1" s="24">
-      <c r="A3" s="30" t="inlineStr">
+    <row r="3" ht="30" customHeight="1" s="24">
+      <c r="A3" s="51" t="inlineStr">
         <is>
           <t>VM atau server</t>
         </is>
       </c>
-      <c r="B3" s="30" t="inlineStr">
+      <c r="B3" s="51" t="inlineStr">
         <is>
           <t>INTERNAL</t>
         </is>
       </c>
-      <c r="C3" s="30" t="n">
+      <c r="C3" s="51" t="n">
         <v>2</v>
       </c>
-      <c r="D3" s="30" t="inlineStr">
+      <c r="D3" s="51" t="inlineStr">
         <is>
           <t>Tidak</t>
         </is>
       </c>
-      <c r="E3" s="30" t="inlineStr">
+      <c r="E3" s="51" t="inlineStr">
         <is>
           <t>Dalam pengadaan</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="15" customHeight="1" s="24">
-      <c r="A4" s="30" t="inlineStr">
+    <row r="4" ht="30" customHeight="1" s="24">
+      <c r="A4" s="51" t="inlineStr">
         <is>
           <t>Layanan cloud atau SaaS</t>
         </is>
       </c>
-      <c r="B4" s="30" t="inlineStr">
+      <c r="B4" s="51" t="inlineStr">
         <is>
           <t>RESTRICTED</t>
         </is>
       </c>
-      <c r="C4" s="30" t="n">
+      <c r="C4" s="51" t="n">
         <v>3</v>
       </c>
-      <c r="E4" s="30" t="inlineStr">
+      <c r="D4" s="52" t="n"/>
+      <c r="E4" s="51" t="inlineStr">
         <is>
           <t>Dinonaktifkan</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1" s="24">
-      <c r="A5" s="30" t="inlineStr">
+    <row r="5" ht="16.5" customHeight="1" s="24">
+      <c r="A5" s="51" t="inlineStr">
         <is>
           <t>Software atau lisensi</t>
         </is>
       </c>
-      <c r="B5" s="30" t="inlineStr">
+      <c r="B5" s="51" t="inlineStr">
         <is>
           <t>SECRET</t>
         </is>
       </c>
-      <c r="E5" s="30" t="inlineStr">
+      <c r="C5" s="52" t="n"/>
+      <c r="D5" s="52" t="n"/>
+      <c r="E5" s="51" t="inlineStr">
         <is>
           <t>Dimusnahkan</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1" s="24">
-      <c r="A6" s="30" t="inlineStr">
+    <row r="6" ht="16.5" customHeight="1" s="24">
+      <c r="A6" s="51" t="inlineStr">
         <is>
           <t>Informasi atau data</t>
         </is>
       </c>
-    </row>
-    <row r="7" ht="15" customHeight="1" s="24">
-      <c r="A7" s="30" t="inlineStr">
+      <c r="B6" s="52" t="n"/>
+      <c r="C6" s="52" t="n"/>
+      <c r="D6" s="52" t="n"/>
+      <c r="E6" s="52" t="n"/>
+    </row>
+    <row r="7" ht="16.5" customHeight="1" s="24">
+      <c r="A7" s="51" t="inlineStr">
         <is>
           <t>Network device</t>
         </is>
       </c>
-    </row>
-    <row r="8" ht="15" customHeight="1" s="24">
-      <c r="A8" s="30" t="inlineStr">
+      <c r="B7" s="52" t="n"/>
+      <c r="C7" s="52" t="n"/>
+      <c r="D7" s="52" t="n"/>
+      <c r="E7" s="52" t="n"/>
+    </row>
+    <row r="8" ht="16.5" customHeight="1" s="24">
+      <c r="A8" s="51" t="inlineStr">
         <is>
           <t>Endpoint</t>
         </is>
       </c>
-    </row>
-    <row r="9" ht="15" customHeight="1" s="24">
-      <c r="A9" s="30" t="inlineStr">
+      <c r="B8" s="52" t="n"/>
+      <c r="C8" s="52" t="n"/>
+      <c r="D8" s="52" t="n"/>
+      <c r="E8" s="52" t="n"/>
+    </row>
+    <row r="9" ht="30" customHeight="1" s="24">
+      <c r="A9" s="51" t="inlineStr">
         <is>
           <t>Domain atau sertifikat</t>
         </is>
       </c>
-    </row>
-    <row r="10" ht="15" customHeight="1" s="24">
-      <c r="A10" s="30" t="inlineStr">
+      <c r="B9" s="52" t="n"/>
+      <c r="C9" s="52" t="n"/>
+      <c r="D9" s="52" t="n"/>
+      <c r="E9" s="52" t="n"/>
+    </row>
+    <row r="10" ht="16.5" customHeight="1" s="24">
+      <c r="A10" s="51" t="inlineStr">
         <is>
           <t>Layanan pihak ketiga</t>
         </is>
       </c>
+      <c r="B10" s="52" t="n"/>
+      <c r="C10" s="52" t="n"/>
+      <c r="D10" s="52" t="n"/>
+      <c r="E10" s="52" t="n"/>
     </row>
   </sheetData>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup orientation="landscape" paperSize="9" scale="100" fitToHeight="0" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
 </worksheet>
 </file>
 
@@ -1315,15 +1486,20 @@
     <col width="16" customWidth="1" style="23" min="5" max="5"/>
     <col width="18" customWidth="1" style="23" min="6" max="6"/>
     <col width="14" customWidth="1" style="23" min="7" max="7"/>
-    <col width="12" customWidth="1" style="23" min="8" max="8"/>
+    <col width="17" customWidth="1" style="23" min="8" max="8"/>
     <col width="4" customWidth="1" style="23" min="9" max="11"/>
-    <col width="7" customWidth="1" style="23" min="12" max="12"/>
-    <col width="9" customWidth="1" style="23" min="13" max="13"/>
+    <col width="13" customWidth="1" style="24" min="10" max="10"/>
+    <col width="13" customWidth="1" style="24" min="11" max="11"/>
+    <col width="8" customWidth="1" style="23" min="12" max="12"/>
+    <col width="18" customWidth="1" style="23" min="13" max="13"/>
     <col width="5" customWidth="1" style="23" min="14" max="14"/>
     <col width="18" customWidth="1" style="23" min="15" max="15"/>
-    <col width="7" customWidth="1" style="23" min="16" max="16"/>
-    <col width="9" customWidth="1" style="23" min="17" max="17"/>
+    <col width="10" customWidth="1" style="23" min="16" max="16"/>
+    <col width="15" customWidth="1" style="23" min="17" max="17"/>
     <col width="11" customWidth="1" style="23" min="18" max="21"/>
+    <col width="13" customWidth="1" style="24" min="19" max="19"/>
+    <col width="13" customWidth="1" style="24" min="20" max="20"/>
+    <col width="15" customWidth="1" style="24" min="21" max="21"/>
     <col width="16" customWidth="1" style="23" min="22" max="22"/>
   </cols>
   <sheetData>
@@ -1341,7 +1517,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="31.5" customHeight="1" s="24">
+    <row r="4" ht="43.5" customHeight="1" s="24">
       <c r="A4" s="39" t="inlineStr">
         <is>
           <t>ID aset</t>
@@ -8515,7 +8691,7 @@
   </dataValidations>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="landscape" paperSize="1" scale="100" fitToHeight="0" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup orientation="landscape" paperSize="8" scale="100" fitToHeight="0" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
 </worksheet>
 </file>
 
@@ -8533,7 +8709,9 @@
     <col width="9" customWidth="1" style="23" min="3" max="3"/>
     <col width="32" customWidth="1" style="23" min="4" max="4"/>
     <col width="22" customWidth="1" style="23" min="5" max="6"/>
+    <col width="13" customWidth="1" style="24" min="6" max="6"/>
     <col width="16" customWidth="1" style="23" min="7" max="8"/>
+    <col width="13" customWidth="1" style="24" min="8" max="8"/>
     <col width="22" customWidth="1" style="23" min="9" max="9"/>
   </cols>
   <sheetData>
@@ -8547,7 +8725,7 @@
     <row r="2" ht="15" customHeight="1" s="24">
       <c r="A2" s="26" t="inlineStr">
         <is>
-          <t>Setiap pemusnahan media atau dekomisi aset dicatat di sini dan status aset di Register Aset diubah menjadi Dimusnahkan.</t>
+          <t>Catat setiap pemusnahan media atau dekomisi aset di sheet ini, lalu ubah status aset di Register Aset menjadi Dimusnahkan.</t>
         </is>
       </c>
     </row>
